--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N78_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.05141443493736</v>
+        <v>12.84585484567732</v>
       </c>
       <c r="D2" t="n">
-        <v>32.40671865351489</v>
+        <v>5.266091781196169</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
